--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 1 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 1 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REKAPITULACIJA LOT 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="LOT 1 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LOT 1 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="REKAPITULACIJA LOT 1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT 1 Sjednica'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOT 1 Sjednica'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOT 1 Sjednica'!$A$1:$F$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'LOT 1 Hamzići'!$8:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'LOT 1 Hamzići'!$A$1:$F$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'LOT 1 Hamzići'!$A$1:$F$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'REKAPITULACIJA LOT 1'!$A$1:$F$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1238,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5.71" customWidth="1" style="91" min="1" max="1"/>
@@ -1392,10 +1392,11 @@
  - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
  - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
  - smještaj: nosači se temelje IZVAN ograđenog platoa, jugozapadno od ograde (JZ strana), cca 0,40 m od ograde; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,83 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥13,3 kN, horizontalna sila ≥10,0 kN, moment prevrtanja ≥25,7 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
+ - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (podizanje, horizontalna sila, moment prevrtanja) proizlaze iz koncepta konstrukcije koji Ponuđač nudi; Ponuđač ih iskazuje i dokazuje u tehničkom rješenju i statičkom proračunu iz Tačke 1.3. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara</t>
+ - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
+ - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
         </is>
       </c>
       <c r="C12" s="113" t="inlineStr">
@@ -1423,9 +1424,9 @@
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
  - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
- - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥13,3 kN (GSN); sila po traci od momenta prevrtanja ≥16,1 kN pri razmaku traka 1600 mm
+ - nosivost i dubina ugradnje: prema ETA za konkretnu podlogu i prema statičkom proračunu iz Tačke 1.3; projektne sile ankerisanja proizlaze iz koncepta konstrukcije koji Ponuđač nudi i iskazuju se u tehničkom rješenju
  - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.3 (dvije trake po nosaču, najmanje 0,74 m³ po traci; tendovano 1,053 m³ po traci) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
+ - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.4 (dvije trake po nosaču, tendovano 1,170 m³ po traci) — dovoljnost vlastite težine i lokalno istezanje trake dokazuju se statičkim proračunom iz Tačke 1.3</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -1451,11 +1452,12 @@
       <c r="B14" s="116" t="inlineStr">
         <is>
           <t>Statički proračun nosive konstrukcije i temelja, ovjeren i potpisan od strane ovlaštenog inženjera.
- - dokaz otpornosti na pritisak vjetra qp ≥ 1,20 kN/m² pri nagibu 45°, prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući orografiju
+ - dokaz na dejstvo vjetra prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući faktor orografije za lokalitet
  - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led 20 mm gustine 300 kg/m³
- - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema EN 1990 (γQ,dst = 1,5; γG,stb = 0,9)
+ - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema BAS EN 1990
+ - dimenzionisanje čelične konstrukcije prema BAS EN 1993-1-1, izvedba prema BAS EN 1090-2
  - dimenzionisanje temelja i sidrenja prema stvarnim geotehničkim uslovima (kamenito tlo), uz navođenje dubine smrzavanja za lokalitet
-NAPOMENA: proračun se dostavlja tokom realizacije kao uslov za primopredaju.</t>
+NAPOMENA: Statički proračun se dostavlja u sklopu tehničkog rješenja i uslov je za počinjanje radova. Prije početka izvođenja radova tehničko rješenje mora biti pregledano i odobreno.</t>
         </is>
       </c>
       <c r="C14" s="117" t="inlineStr">
@@ -1566,7 +1568,7 @@
       </c>
       <c r="B20" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
         </is>
       </c>
       <c r="C20" s="130" t="inlineStr">
@@ -1589,9 +1591,9 @@
           <t>2.2</t>
         </is>
       </c>
-      <c r="B21" s="132" t="inlineStr">
-        <is>
-          <t>Zatrpavanje preostalog dijela rova zemljom od iskopa uz nabijanje u slojevima. Traka je pune dubine, pa se zatrpava samo klin uz kosinu rova. 4 nosača × 2 trake × 0,117 m3</t>
+      <c r="B21" s="129" t="inlineStr">
+        <is>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 1,235 m3</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -1600,7 +1602,7 @@
         </is>
       </c>
       <c r="D21" s="130" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131">
@@ -1611,12 +1613,12 @@
     <row r="22" s="92">
       <c r="A22" s="128" t="inlineStr">
         <is>
-          <t>2.2a</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B22" s="129" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km.</t>
+          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
         </is>
       </c>
       <c r="C22" s="130" t="inlineStr">
@@ -1625,7 +1627,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>8.94</v>
+        <v>0.52</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -1636,12 +1638,13 @@
     <row r="23" s="92">
       <c r="A23" s="128" t="inlineStr">
         <is>
-          <t>2.2b</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B23" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci. 4 nosača × 2 trake × 1,170 m³
+BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova i do zida rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje. Temelj širi u dnu nego u vrhu tražio bi potkopavanje i u stijeni nije izvodiv, pa je presjek jedinstven.</t>
         </is>
       </c>
       <c r="C23" s="130" t="inlineStr">
@@ -1650,7 +1653,7 @@
         </is>
       </c>
       <c r="D23" s="130" t="n">
-        <v>0.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E23" s="131" t="n"/>
       <c r="F23" s="131">
@@ -1661,22 +1664,21 @@
     <row r="24" s="92">
       <c r="A24" s="128" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B24" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 400 mm (gore) / 500 mm (dolje) × 2600 mm, PUNE dubine 900 mm = 1,053 m³ po traci. 4 nosača × 2 trake × 1,053 m³
-BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje.</t>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. 0,50 × 2,60 × 8 traka = 10,4 m².</t>
         </is>
       </c>
       <c r="C24" s="130" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D24" s="130" t="n">
-        <v>8.42</v>
+        <v>10.4</v>
       </c>
       <c r="E24" s="131" t="n"/>
       <c r="F24" s="131">
@@ -1687,21 +1689,21 @@
     <row r="25" s="92">
       <c r="A25" s="128" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B25" s="129" t="inlineStr">
-        <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja.</t>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B25" s="132" t="inlineStr">
+        <is>
+          <t>Ostali sitni građevinski i potrošni materijal.</t>
         </is>
       </c>
       <c r="C25" s="130" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>paušal</t>
         </is>
       </c>
       <c r="D25" s="130" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E25" s="131" t="n"/>
       <c r="F25" s="131">
@@ -1709,59 +1711,34 @@
         <v/>
       </c>
     </row>
-    <row r="26" s="92">
-      <c r="A26" s="128" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B26" s="132" t="inlineStr">
-        <is>
-          <t>Ostali sitni građevinski i potrošni materijal.</t>
-        </is>
-      </c>
-      <c r="C26" s="130" t="inlineStr">
-        <is>
-          <t>paušal</t>
-        </is>
-      </c>
-      <c r="D26" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="131" t="n"/>
-      <c r="F26" s="131">
-        <f>IF(AND(D26&lt;&gt;"",E26&lt;&gt;""),D26*E26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="92">
-      <c r="A27" s="135" t="n"/>
-      <c r="B27" s="135" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="92">
+      <c r="A26" s="135" t="n"/>
+      <c r="B26" s="135" t="inlineStr">
         <is>
           <t>UKUPNO 2 — GRAĐEVINSKI RADOVI ZA NOSAČE FN PANELA:</t>
         </is>
       </c>
-      <c r="C27" s="136" t="n"/>
-      <c r="D27" s="136" t="n"/>
-      <c r="E27" s="137" t="n"/>
-      <c r="F27" s="138">
-        <f>SUM(F20:F26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" s="92"/>
-    <row r="29" ht="15" customHeight="1" s="92">
-      <c r="A29" s="139" t="n"/>
-      <c r="B29" s="139" t="inlineStr">
+      <c r="C26" s="136" t="n"/>
+      <c r="D26" s="136" t="n"/>
+      <c r="E26" s="137" t="n"/>
+      <c r="F26" s="138">
+        <f>SUM(F20:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" s="92"/>
+    <row r="28" ht="15" customHeight="1" s="92">
+      <c r="A28" s="139" t="n"/>
+      <c r="B28" s="139" t="inlineStr">
         <is>
           <t>UKUPNO LOT 1 — BS SJEDNICA (bez PDV-a):</t>
         </is>
       </c>
-      <c r="C29" s="136" t="n"/>
-      <c r="D29" s="137" t="n"/>
-      <c r="E29" s="137" t="n"/>
-      <c r="F29" s="140">
-        <f>F18+F27</f>
+      <c r="C28" s="136" t="n"/>
+      <c r="D28" s="137" t="n"/>
+      <c r="E28" s="137" t="n"/>
+      <c r="F28" s="140">
+        <f>F18+F26</f>
         <v/>
       </c>
     </row>
@@ -1790,7 +1767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5.71" customWidth="1" style="91" min="1" max="1"/>
@@ -1944,10 +1921,11 @@
  - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Listopadno stablo JJI–JI od stuba (≈7–9 m, 15–20 m, izvan zakupa) ostaje; pri polju okrenutom prema jugozapadu njegov uticaj je mali (Prilog I, Tačka 3.7)
  - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
  - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,93 m iznad vrha ograde — ograda je h=1,80 m iznad ploče, odnosno 2,00 m iznad vanjskog terena, koji je uz ploču na −0,20 m (ovjereni 04_Ograda). Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupa 12,00 × 12,50 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom — ista vrijednost kao na lokaciji Sjednica, radi jedne konstrukcije za obje lokacije (iz ovjerenog projekta lokacije, 493 m n.v., izvodi se 0,69–0,96 kN/m²). Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥13,3 kN, horizontalna sila ≥10,0 kN, moment prevrtanja ≥25,7 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju ako se ipak nudi kataloški proizvod
+ - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom — ista vrijednost kao na lokaciji Sjednica, radi jedne konstrukcije za obje lokacije (iz ovjerenog projekta lokacije, 493 m n.v., izvodi se 0,69–0,96 kN/m²). Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (podizanje, horizontalna sila, moment prevrtanja) proizlaze iz koncepta konstrukcije koji Ponuđač nudi; Ponuđač ih iskazuje i dokazuje u tehničkom rješenju i statičkom proračunu iz Tačke 1.3. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež H-05): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara</t>
+ - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež H-05): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
+ - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
         </is>
       </c>
       <c r="C12" s="113" t="inlineStr">
@@ -1975,9 +1953,9 @@
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
  - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
- - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥13,3 kN (GSN); sila po traci od momenta prevrtanja ≥16,1 kN pri razmaku traka 1600 mm
+ - nosivost i dubina ugradnje: prema ETA za konkretnu podlogu i prema statičkom proračunu iz Tačke 1.3; projektne sile ankerisanja proizlaze iz koncepta konstrukcije koji Ponuđač nudi i iskazuju se u tehničkom rješenju
  - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.3 (dvije trake po nosaču, najmanje 0,74 m³ po traci; tendovano 1,053 m³ po traci) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
+ - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.4 (dvije trake po nosaču, tendovano 1,170 m³ po traci) — dovoljnost vlastite težine i lokalno istezanje trake dokazuju se statičkim proračunom iz Tačke 1.3</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -2003,11 +1981,12 @@
       <c r="B14" s="116" t="inlineStr">
         <is>
           <t>Statički proračun nosive konstrukcije i temelja, ovjeren i potpisan od strane ovlaštenog inženjera.
- - dokaz otpornosti na pritisak vjetra qp ≥ 1,20 kN/m² pri nagibu 45°, prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući orografiju
+ - dokaz na dejstvo vjetra prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući faktor orografije za lokalitet
  - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led 20 mm gustine 300 kg/m³
- - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema EN 1990 (γQ,dst = 1,5; γG,stb = 0,9)
+ - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema BAS EN 1990
+ - dimenzionisanje čelične konstrukcije prema BAS EN 1993-1-1, izvedba prema BAS EN 1090-2
  - dimenzionisanje temelja i sidrenja prema stvarnim geotehničkim uslovima (kamenito tlo), uz navođenje dubine smrzavanja za lokalitet
-NAPOMENA: proračun se dostavlja tokom realizacije kao uslov za primopredaju.</t>
+NAPOMENA: Statički proračun se dostavlja u sklopu tehničkog rješenja i uslov je za počinjanje radova. Prije početka izvođenja radova tehničko rješenje mora biti pregledano i odobreno.</t>
         </is>
       </c>
       <c r="C14" s="117" t="inlineStr">
@@ -2143,7 +2122,7 @@
       </c>
       <c r="B21" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -2166,9 +2145,9 @@
           <t>2.2</t>
         </is>
       </c>
-      <c r="B22" s="132" t="inlineStr">
-        <is>
-          <t>Zatrpavanje preostalog dijela rova zemljom od iskopa uz nabijanje u slojevima. Traka je pune dubine, pa se zatrpava samo klin uz kosinu rova. 4 nosača × 2 trake × 0,117 m3</t>
+      <c r="B22" s="129" t="inlineStr">
+        <is>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 1,235 m3</t>
         </is>
       </c>
       <c r="C22" s="130" t="inlineStr">
@@ -2177,7 +2156,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>0.9399999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -2188,12 +2167,12 @@
     <row r="23" s="92">
       <c r="A23" s="128" t="inlineStr">
         <is>
-          <t>2.2a</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B23" s="129" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km.</t>
+          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
         </is>
       </c>
       <c r="C23" s="130" t="inlineStr">
@@ -2202,7 +2181,7 @@
         </is>
       </c>
       <c r="D23" s="130" t="n">
-        <v>8.94</v>
+        <v>0.52</v>
       </c>
       <c r="E23" s="131" t="n"/>
       <c r="F23" s="131">
@@ -2213,12 +2192,13 @@
     <row r="24" s="92">
       <c r="A24" s="128" t="inlineStr">
         <is>
-          <t>2.2b</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B24" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 4 nosača × 2 trake × 0,065 m3</t>
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci. 4 nosača × 2 trake × 1,170 m³
+BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3: ista specifikacija kao na lokaciji Sjednica, radi jednog opisa za obje lokacije. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova i do zida rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje. Temelj širi u dnu nego u vrhu tražio bi potkopavanje i u stijeni nije izvodiv, pa je presjek jedinstven.</t>
         </is>
       </c>
       <c r="C24" s="130" t="inlineStr">
@@ -2227,7 +2207,7 @@
         </is>
       </c>
       <c r="D24" s="130" t="n">
-        <v>0.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E24" s="131" t="n"/>
       <c r="F24" s="131">
@@ -2238,22 +2218,21 @@
     <row r="25" s="92">
       <c r="A25" s="128" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B25" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 400 mm (gore) / 500 mm (dolje) × 2600 mm, PUNE dubine 900 mm = 1,053 m³ po traci. 4 nosača × 2 trake × 1,053 m³
-BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3: ista specifikacija kao na lokaciji Sjednica, radi jednog opisa za obje lokacije. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje.</t>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. 0,50 × 2,60 × 8 traka = 10,4 m².</t>
         </is>
       </c>
       <c r="C25" s="130" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D25" s="130" t="n">
-        <v>8.42</v>
+        <v>10.4</v>
       </c>
       <c r="E25" s="131" t="n"/>
       <c r="F25" s="131">
@@ -2264,21 +2243,21 @@
     <row r="26" s="92">
       <c r="A26" s="128" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B26" s="129" t="inlineStr">
-        <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja.</t>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B26" s="132" t="inlineStr">
+        <is>
+          <t>Ostali sitni građevinski i potrošni materijal.</t>
         </is>
       </c>
       <c r="C26" s="130" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>paušal</t>
         </is>
       </c>
       <c r="D26" s="130" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E26" s="131" t="n"/>
       <c r="F26" s="131">
@@ -2286,59 +2265,34 @@
         <v/>
       </c>
     </row>
-    <row r="27" s="92">
-      <c r="A27" s="128" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B27" s="132" t="inlineStr">
-        <is>
-          <t>Ostali sitni građevinski i potrošni materijal.</t>
-        </is>
-      </c>
-      <c r="C27" s="130" t="inlineStr">
-        <is>
-          <t>paušal</t>
-        </is>
-      </c>
-      <c r="D27" s="130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="131" t="n"/>
-      <c r="F27" s="131">
-        <f>IF(AND(D27&lt;&gt;"",E27&lt;&gt;""),D27*E27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="92">
-      <c r="A28" s="135" t="n"/>
-      <c r="B28" s="135" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="92">
+      <c r="A27" s="135" t="n"/>
+      <c r="B27" s="135" t="inlineStr">
         <is>
           <t>UKUPNO 2 — GRAĐEVINSKI RADOVI ZA NOSAČE FN PANELA:</t>
         </is>
       </c>
-      <c r="C28" s="136" t="n"/>
-      <c r="D28" s="136" t="n"/>
-      <c r="E28" s="137" t="n"/>
-      <c r="F28" s="138">
-        <f>SUM(F21:F27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" s="92"/>
-    <row r="30" ht="15" customHeight="1" s="92">
-      <c r="A30" s="139" t="n"/>
-      <c r="B30" s="139" t="inlineStr">
+      <c r="C27" s="136" t="n"/>
+      <c r="D27" s="136" t="n"/>
+      <c r="E27" s="137" t="n"/>
+      <c r="F27" s="138">
+        <f>SUM(F21:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" s="92"/>
+    <row r="29" ht="15" customHeight="1" s="92">
+      <c r="A29" s="139" t="n"/>
+      <c r="B29" s="139" t="inlineStr">
         <is>
           <t>UKUPNO LOT 1 — BS HAMZIĆI (bez PDV-a):</t>
         </is>
       </c>
-      <c r="C30" s="136" t="n"/>
-      <c r="D30" s="137" t="n"/>
-      <c r="E30" s="137" t="n"/>
-      <c r="F30" s="140">
-        <f>F19+F28</f>
+      <c r="C29" s="136" t="n"/>
+      <c r="D29" s="137" t="n"/>
+      <c r="E29" s="137" t="n"/>
+      <c r="F29" s="140">
+        <f>F19+F27</f>
         <v/>
       </c>
     </row>
@@ -2446,7 +2400,7 @@
       <c r="D10" s="168" t="n"/>
       <c r="E10" s="137" t="n"/>
       <c r="F10" s="172">
-        <f>'LOT 1 Sjednica'!F29</f>
+        <f>'LOT 1 Sjednica'!F28</f>
         <v/>
       </c>
     </row>
@@ -2461,7 +2415,7 @@
       <c r="D11" s="168" t="n"/>
       <c r="E11" s="137" t="n"/>
       <c r="F11" s="172">
-        <f>'LOT 1 Hamzići'!F30</f>
+        <f>'LOT 1 Hamzići'!F29</f>
         <v/>
       </c>
     </row>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LOT 1 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LOT 1 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="REKAPITULACIJA LOT 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 1 Sjednica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOT 1 Hamzići" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REKAPITULACIJA LOT 1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'LOT 1 Sjednica'!$8:$9</definedName>

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
@@ -1387,14 +1387,12 @@
       </c>
       <c r="B12" s="112" t="inlineStr">
         <is>
-          <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela, karakteristika:
- - tip: CUSTOM IZRADA (izvan kataloga zbog opterećenja vjetrom, v. niže) — 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); odvojeni nosači umjesto jednog velikog polja smanjuju silu vjetra po konstrukciji (zahtjev Naručioca); geometrija margina/prepusta preuzeta iz Huawei Standard A-Shaped Support 3.0 konvencije (PVM Tabela 4-20), ali poprečna greda izrađena po mjeri za 1 kolonu položenih modula, ne za kataloških 6
- - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
- - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
- - smještaj: nosači se temelje IZVAN ograđenog platoa, jugozapadno od ograde (JZ strana), cca 0,40 m od ograde; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,83 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (podizanje, horizontalna sila, moment prevrtanja) proizlaze iz koncepta konstrukcije koji Ponuđač nudi; Ponuđač ih iskazuje i dokazuje u tehničkom rješenju i statičkom proračunu iz Tačke 1.3. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
- - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
- - spojni pribor: nehrđajući čelik A2/A4
+          <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela:
+ - 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); razmak između nosača 400 mm, dužina niza 10 312 mm
+ - nagib fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom
+ - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena
+ - smještaj: nosači se temelje IZVAN ograđenog platoa, jugozapadno od ograde (JZ strana), cca 0,40 m od ograde; odmak od ograde Ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,83 m iznad kote ograde h=2,10 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
+ - materijal, antikorozivna zaštita, zavarivanje i spojni pribor prema Prilogu I, Tačka 3.3
  - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
  - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
         </is>
@@ -1423,10 +1421,9 @@
         <is>
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
- - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
+ - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču
  - nosivost i dubina ugradnje: prema ETA za konkretnu podlogu i prema statičkom proračunu iz Tačke 1.3; projektne sile ankerisanja proizlaze iz koncepta konstrukcije koji Ponuđač nudi i iskazuju se u tehničkom rješenju
- - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.4 (dvije trake po nosaču, tendovano 1,170 m³ po traci) — dovoljnost vlastite težine i lokalno istezanje trake dokazuju se statičkim proračunom iz Tačke 1.3</t>
+ - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 2 ankera po lokaciji, do 1,5 × projektne sile iz odobrenog tehničkog rješenja, uz zapisnik ovjeren od nadzornog organa</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -1453,7 +1450,7 @@
         <is>
           <t>Statički proračun nosive konstrukcije i temelja, ovjeren i potpisan od strane ovlaštenog inženjera.
  - dokaz na dejstvo vjetra prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući faktor orografije za lokalitet
- - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led 20 mm gustine 300 kg/m³
+ - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led prema ovjerenoj projektnoj dokumentaciji lokacije
  - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema BAS EN 1990
  - dimenzionisanje čelične konstrukcije prema BAS EN 1993-1-1, izvedba prema BAS EN 1090-2
  - dimenzionisanje temelja i sidrenja prema stvarnim geotehničkim uslovima (kamenito tlo), uz navođenje dubine smrzavanja za lokalitet
@@ -1916,14 +1913,12 @@
       </c>
       <c r="B12" s="112" t="inlineStr">
         <is>
-          <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela, karakteristika:
- - tip: CUSTOM IZRADA (izvan kataloga zbog opterećenja vjetrom, v. niže) — 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); odvojeni nosači umjesto jednog velikog polja smanjuju silu vjetra po konstrukciji (zahtjev Naručioca); geometrija margina/prepusta preuzeta iz Huawei Standard A-Shaped Support 3.0 konvencije (PVM Tabela 4-20), ali poprečna greda izrađena po mjeri za 1 kolonu položenih modula, ne za kataloških 6
- - inklinacija: fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom (Naručilac 11.09.2026). Listopadno stablo JJI–JI od stuba (≈7–9 m, 15–20 m, izvan zakupa) ostaje; pri polju okrenutom prema jugozapadu njegov uticaj je mali (Prilog I, Tačka 3.7)
- - gabariti PV polja po nosaču (3 reda × 1 modul, položeno): širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm (3 × 1134 mm + 2 × 20 mm), horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena; razmak između nosača 400 mm, dužina niza 10 312 mm
- - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; odmak od ograde ponuđač utvrđuje pri poziciranju nosača tako da ravan panela nigdje ne dodiruje ogradu; gornja (sjeveroistočna) ivica panela je 0,93 m iznad vrha ograde — ograda je h=1,80 m iznad ploče, odnosno 2,00 m iznad vanjskog terena, koji je uz ploču na −0,20 m (ovjereni 04_Ograda). Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupa 12,00 × 12,50 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom — ista vrijednost kao na lokaciji Sjednica, radi jedne konstrukcije za obje lokacije (iz ovjerenog projekta lokacije, 493 m n.v., izvodi se 0,69–0,96 kN/m²). Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 7,84 m² po nosaču (2278 × 3442 mm). Projektne sile po nosaču (podizanje, horizontalna sila, moment prevrtanja) proizlaze iz koncepta konstrukcije koji Ponuđač nudi; Ponuđač ih iskazuje i dokazuje u tehničkom rješenju i statičkom proračunu iz Tačke 1.3. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju ako se ipak nudi kataloški proizvod
- - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
- - spojni pribor: nehrđajući čelik A2/A4
+          <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela:
+ - 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); razmak između nosača 400 mm, dužina niza 10 312 mm
+ - nagib fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom
+ - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena
+ - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; gornja (sjeveroistočna) ivica panela je 0,93 m iznad vrha ograde — ograda je h=1,80 m iznad ploče, odnosno 2,00 m iznad vanjskog terena, koji je uz ploču na −0,20 m (ovjereni 04_Ograda)
+ - materijal, antikorozivna zaštita, zavarivanje i spojni pribor prema Prilogu I, Tačka 3.3
  - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež H-05): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
  - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
         </is>
@@ -1952,10 +1947,9 @@
         <is>
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
- - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
+ - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču
  - nosivost i dubina ugradnje: prema ETA za konkretnu podlogu i prema statičkom proračunu iz Tačke 1.3; projektne sile ankerisanja proizlaze iz koncepta konstrukcije koji Ponuđač nudi i iskazuju se u tehničkom rješenju
- - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj iz Tačke 2.4 (dvije trake po nosaču, tendovano 1,170 m³ po traci) — dovoljnost vlastite težine i lokalno istezanje trake dokazuju se statičkim proračunom iz Tačke 1.3</t>
+ - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 2 ankera po lokaciji, do 1,5 × projektne sile iz odobrenog tehničkog rješenja, uz zapisnik ovjeren od nadzornog organa</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
@@ -1982,7 +1976,7 @@
         <is>
           <t>Statički proračun nosive konstrukcije i temelja, ovjeren i potpisan od strane ovlaštenog inženjera.
  - dokaz na dejstvo vjetra prema BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uključujući faktor orografije za lokalitet
- - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led 20 mm gustine 300 kg/m³
+ - dokaz na opterećenje snijegom prema BAS EN 1991-1-3 i na radijalni led prema ovjerenoj projektnoj dokumentaciji lokacije
  - dokaz sigurnosti na podizanje (uplift) i prevrtanje prema BAS EN 1990
  - dimenzionisanje čelične konstrukcije prema BAS EN 1993-1-1, izvedba prema BAS EN 1090-2
  - dimenzionisanje temelja i sidrenja prema stvarnim geotehničkim uslovima (kamenito tlo), uz navođenje dubine smrzavanja za lokalitet

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
@@ -1916,8 +1916,8 @@
           <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela:
  - 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); razmak između nosača 400 mm, dužina niza 10 312 mm
  - nagib fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom
- - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena
- - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; gornja (sjeveroistočna) ivica panela je 0,93 m iznad vrha ograde — ograda je h=1,80 m iznad ploče, odnosno 2,00 m iznad vanjskog terena, koji je uz ploču na −0,20 m (ovjereni 04_Ograda)
+ - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od gornje ivice ploče, u čijem je nivou vrh temeljnih traka
+ - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; vrh temeljnih traka je u nivou gornje ivice ploče, 0,20 m iznad vanjskog terena (teren uz ploču je na −0,20 m, ovjereni 04_Ograda); gornja (sjeveroistočna) ivica panela je 1,13 m iznad vrha ograde h=1,80 m od ploče
  - materijal, antikorozivna zaštita, zavarivanje i spojni pribor prema Prilogu I, Tačka 3.3
  - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež H-05): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
  - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B21" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 750 mm od vanjskog terena, dužine 2600 mm (vrh trake je 0,20 m iznad terena, u nivou ploče). 4 nosača × 2 trake × 0,975 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="D21" s="130" t="n">
-        <v>9.880000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B22" s="129" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 1,235 m3</t>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 0,975 m3</t>
         </is>
       </c>
       <c r="C22" s="130" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>9.880000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B24" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci. 4 nosača × 2 trake × 1,170 m³
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci; vrh trake je u nivou gornje ivice ploče, 0,20 m iznad vanjskog terena, pa se gornjih 200 mm betonira u oplati. 4 nosača × 2 trake × 1,170 m³
 BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3: ista specifikacija kao na lokaciji Sjednica, radi jednog opisa za obje lokacije. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova i do zida rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje. Temelj širi u dnu nego u vrhu tražio bi potkopavanje i u stijeni nije izvodiv, pa je presjek jedinstven.</t>
         </is>
       </c>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B25" s="129" t="inlineStr">
         <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. 0,50 × 2,60 × 8 traka = 10,4 m².</t>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. Gornja površina 0,50 × 2,60 × 8 traka = 10,4 m² i bočne strane iznad terena 2 × (2,60 + 0,50) × 0,20 × 8 traka = 9,9 m², ukupno 20,3 m².</t>
         </is>
       </c>
       <c r="C25" s="130" t="inlineStr">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="D25" s="130" t="n">
-        <v>10.4</v>
+        <v>20.3</v>
       </c>
       <c r="E25" s="131" t="n"/>
       <c r="F25" s="131">

--- a/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
+++ b/rfp-hybrid-solar-td/TD-OUTPUT/3.1 PRILOG II TD - Obrazac za cijenu ponude LOT 1 - Sjednica i Hamzici.xlsx
@@ -1916,8 +1916,8 @@
           <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela:
  - 4 odvojena nosača u jednom nizu, svaki za 3 fotonaponska modula (3 reda × 1 kolona, položeno); razmak između nosača 400 mm, dužina niza 10 312 mm
  - nagib fiksno 45°, orijentacija JUGOZAPAD (azimut 225°), niz paralelan sa jugozapadnom ogradom
- - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od gornje ivice ploče, u čijem je nivou vrh temeljnih traka
- - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; vrh temeljnih traka je u nivou gornje ivice ploče, 0,20 m iznad vanjskog terena (teren uz ploču je na −0,20 m, ovjereni 04_Ograda); gornja (sjeveroistočna) ivica panela je 1,13 m iznad vrha ograde h=1,80 m od ploče
+ - gabariti po nosaču: širina polja 2278 mm (poprečna greda 2891 mm, bočni prepust 306,5 mm), dužina polja po nagibu 3442 mm, horizontalna projekcija 2434 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +2,93 m od nivoa terena
+ - smještaj (43,288012° N, 17,624794° E, 493 m n.v.): nosači se temelje IZVAN ograđenog platoa, jugozapadno od ploče i ograde, u pojasu dubine 3300 mm i dužine 12,50 m (JZ strana), unutar zakupa k.č. 109/1 K.O. Hamzići (12,00 × 12,50 m); trake 350 mm od granice zakupa i od ploče; gornja (sjeveroistočna) ivica panela je 0,93 m iznad vrha ograde — ograda je h=1,80 m iznad ploče, odnosno 2,00 m iznad vanjskog terena, koji je uz ploču na −0,20 m (ovjereni 04_Ograda)
  - materijal, antikorozivna zaštita, zavarivanje i spojni pribor prema Prilogu I, Tačka 3.3
  - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. crtež H-05): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-3 i PV-4), po jedan string na svaku od dvije rute PVDB ormara
  - UZ PONUDU: Ponuđač je obavezan da uz ponudu dostavi tehničko rješenje konstrukcije za prihvat fotonaponskih panela za predmetnu lokaciju, sa obaveznim statičkim proračunom (Tačka 1.3) i specifikacijom materijala. Tehničko rješenje mora biti pregledano i odobreno prije početka izvođenja radova</t>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B21" s="129" t="inlineStr">
         <is>
-          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 750 mm od vanjskog terena, dužine 2600 mm (vrh trake je 0,20 m iznad terena, u nivou ploče). 4 nosača × 2 trake × 0,975 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
+          <t>Iskop zemlje/stijene IV-V kategorije za temeljne trake nosača, do donje ivice podložnog betona. Rov širine 500 mm, dubine 950 mm, dužine 2600 mm. 4 nosača × 2 trake × 1,235 m3. Rov se u stijeni siječe jednom širinom po cijeloj dubini; traka se betonira do zida rova, pa zatrpavanja nema.</t>
         </is>
       </c>
       <c r="C21" s="130" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="D21" s="130" t="n">
-        <v>7.8</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B22" s="129" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 0,975 m3</t>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km. Traka i podložni beton ispunjavaju rov u cijelosti, pa se odvozi sav iskopani materijal. 4 nosača × 2 trake × 1,235 m3</t>
         </is>
       </c>
       <c r="C22" s="130" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D22" s="130" t="n">
-        <v>7.8</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="E22" s="131" t="n"/>
       <c r="F22" s="131">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B24" s="129" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci; vrh trake je u nivou gornje ivice ploče, 0,20 m iznad vanjskog terena, pa se gornjih 200 mm betonira u oplati. 4 nosača × 2 trake × 1,170 m³
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. Traka 500 × 2600 mm, jedinstvene širine po cijeloj dubini (bez proširenja u dnu), PUNE dubine 900 mm = 1,170 m³ po traci. 4 nosača × 2 trake × 1,170 m³
 BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3: ista specifikacija kao na lokaciji Sjednica, radi jednog opisa za obje lokacije. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina 900 mm je tenderska osnova i mjerodavna je za ponudu; konačnu dubinu i armaturu potvrđuje ovjereni statički proračun iz Tačke 1.3. Traka se betonira punom dubinom rova i do zida rova — vlastita težina trake je dio dokaza sigurnosti na podizanje i prevrtanje. Temelj širi u dnu nego u vrhu tražio bi potkopavanje i u stijeni nije izvodiv, pa je presjek jedinstven.</t>
         </is>
       </c>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B25" s="129" t="inlineStr">
         <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. Gornja površina 0,50 × 2,60 × 8 traka = 10,4 m² i bočne strane iznad terena 2 × (2,60 + 0,50) × 0,20 × 8 traka = 9,9 m², ukupno 20,3 m².</t>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja. 0,50 × 2,60 × 8 traka = 10,4 m².</t>
         </is>
       </c>
       <c r="C25" s="130" t="inlineStr">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="D25" s="130" t="n">
-        <v>20.3</v>
+        <v>10.4</v>
       </c>
       <c r="E25" s="131" t="n"/>
       <c r="F25" s="131">
